--- a/External Files/Flipper Ticklist.xlsx
+++ b/External Files/Flipper Ticklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\The-Flipper-Framework\Production\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Bumper-Engine-2\External Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78087C9A-8D74-4F3D-A33C-658F634E9040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C02EF38-0AE4-4A39-B545-54B721DB5B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="660" windowWidth="19440" windowHeight="14880" xr2:uid="{85BE2389-3B13-409D-8678-A22E603B8D44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{85BE2389-3B13-409D-8678-A22E603B8D44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -624,7 +624,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{86410C58-6B6D-4EED-9E65-FD2E7F3EE110}" name="Table1" displayName="Table1" ref="A3:H21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A3:H21" xr:uid="{86410C58-6B6D-4EED-9E65-FD2E7F3EE110}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H21">
-    <sortCondition descending="1" ref="G3:G21"/>
+    <sortCondition descending="1" ref="F3:F21"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="20" xr3:uid="{EEB40BCE-3B8E-47D1-81A3-95F808EEC662}" name="Category" dataDxfId="15"/>
@@ -943,30 +943,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R133"/>
-  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="31.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="26.28515625" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="31.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" customWidth="1"/>
+    <col min="18" max="18" width="26.33203125" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
@@ -988,7 +988,7 @@
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
     </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -1047,23 +1047,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" ref="G4:G21" si="0">SUM(F4 - E4)</f>
+        <f>SUM(F4 - E4)</f>
         <v>3</v>
       </c>
       <c r="H4" s="9" t="s">
@@ -1079,12 +1079,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1092,14 +1092,14 @@
         <v>2</v>
       </c>
       <c r="F5" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(F5 - E5)</f>
+        <v>3</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" t="s">
         <v>15</v>
@@ -1111,7 +1111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
@@ -1127,11 +1127,11 @@
         <v>5</v>
       </c>
       <c r="G6" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F6 - E6)</f>
         <v>2</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="s">
         <v>12</v>
@@ -1140,27 +1140,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(F7 - E7)</f>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" t="s">
         <v>26</v>
@@ -1169,77 +1169,81 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>26</v>
+    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>0</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
       <c r="E8" s="13">
         <v>3</v>
       </c>
       <c r="F8" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(F8 - E8)</f>
+        <v>2</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="13">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <v>4</v>
+      </c>
+      <c r="G9" s="13">
+        <f>SUM(F9 - E9)</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="13">
-        <v>2</v>
-      </c>
-      <c r="F9" s="13">
-        <v>3</v>
-      </c>
-      <c r="G9" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="B10" s="12" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="E10" s="13">
+        <v>2</v>
+      </c>
+      <c r="F10" s="13">
+        <v>4</v>
+      </c>
       <c r="G10" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F10 - E10)</f>
+        <v>2</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1247,68 +1251,68 @@
         <v>3</v>
       </c>
       <c r="F11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F11 - E11)</f>
+        <v>1</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F12 - E12)</f>
+        <v>1</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F13 - E13)</f>
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1319,114 +1323,114 @@
         <v>4</v>
       </c>
       <c r="G14" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F14 - E14)</f>
         <v>0</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>26</v>
+    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
       <c r="E15" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F15 - E15)</f>
+        <v>1</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="13">
         <f>SUM(F16 - E16)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>0</v>
+    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+        <v>18</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F17 - E17)</f>
+        <v>-1</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F18 - E18)</f>
         <v>-1</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="13">
         <v>3</v>
       </c>
@@ -1434,37 +1438,37 @@
         <v>2</v>
       </c>
       <c r="G19" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F19 - E19)</f>
         <v>-1</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>11</v>
+    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+        <v>28</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="13">
-        <f t="shared" si="0"/>
-        <v>-1</v>
+        <f>SUM(F20 - E20)</f>
+        <v>0</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
@@ -1480,63 +1484,63 @@
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(F21 - E21)</f>
         <v>-2</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="1"/>
     </row>
-    <row r="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
@@ -1548,7 +1552,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="2"/>
     </row>
-    <row r="117" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I117" s="1"/>
       <c r="J117" s="3"/>
       <c r="K117" s="1"/>
@@ -1560,7 +1564,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
-    <row r="118" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -1572,7 +1576,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
     </row>
-    <row r="119" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
@@ -1584,32 +1588,32 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
     </row>
-    <row r="122" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="130" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F130" s="1"/>
     </row>
-    <row r="131" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F131" s="1"/>
     </row>
-    <row r="132" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F132" s="1"/>
     </row>
-    <row r="133" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="6:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F133" s="1"/>
     </row>
   </sheetData>
